--- a/primechop_audit.xlsx
+++ b/primechop_audit.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,37 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6402550456</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ilekuba Collins</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WAI614</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-04-09T19:35:45.230427+01:00</t>
         </is>
       </c>
     </row>

--- a/primechop_audit.xlsx
+++ b/primechop_audit.xlsx
@@ -551,18 +551,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>waiter</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-09T19:35:45.230427+01:00</t>
+          <t>2026-04-09T22:41:04.581902+01:00</t>
         </is>
       </c>
     </row>
